--- a/proposals/farmers-coop/MCE Tub Plant Payback Calculator - Farmers Cooperative.xlsx
+++ b/proposals/farmers-coop/MCE Tub Plant Payback Calculator - Farmers Cooperative.xlsx
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>1517299</v>
+        <v>1758850</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
